--- a/results/job_matches_2026-10-04.xlsx
+++ b/results/job_matches_2026-10-04.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,17 +456,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SENIOR DATA ENGINEER</t>
+          <t>API &amp; Data Engineer II</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>US Neuro LLC</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -474,77 +474,77 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, SQL Server</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5acff10101632d23</t>
+          <t>https://www.indeed.com/viewjob?jk=a3babb1e30d3465d</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>API &amp; Data Engineer II</t>
+          <t>Sr. Cloud Ops Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>SpyCloud</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15.3</v>
+        <v>11.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Databricks, Scala, Snowflake, DynamoDB</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3babb1e30d3465d</t>
+          <t>https://www.indeed.com/viewjob?jk=e7d5eebfd52c3041</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Software Engineer III - AWS, Databricks, Python</t>
+          <t>Government and Infrastructure - Cybersecurity - DevSecOps Senior Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.3</v>
+        <v>11.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Databricks, Spark, PySpark, Scala</t>
+          <t>RDS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Jenkins</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -554,32 +554,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54895b1eb093622c</t>
+          <t>https://www.indeed.com/viewjob?jk=8204bb14afee5287</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Guidewire Engineer (PolicyCenter)</t>
+          <t>Government and Infrastructure - Cybersecurity - DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Mercury Insurance Company</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Jenkins</t>
+          <t>RDS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Jenkins</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -589,357 +589,42 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09a5908bdb474bc4</t>
+          <t>https://www.indeed.com/viewjob?jk=4f386708dcb9013c</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sr. Cloud Ops Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SpyCloud</t>
+          <t>Slalom Consulting</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Databricks, Scala, Snowflake, DynamoDB</t>
+          <t>AWS, S3, API Gateway, IAM, RDS, Azure, GCP, Scala, Snowflake, Azure DevOps</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7d5eebfd52c3041</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Government and Infrastructure - Cybersecurity - DevSecOps Senior Engineer</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>EY</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>McLean, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>RDS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Jenkins</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8204bb14afee5287</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Government and Infrastructure - Cybersecurity - DevSecOps Engineer</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>EY</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>McLean, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>RDS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Jenkins</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4f386708dcb9013c</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Senior Full Stack Software Engineer</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Fannie Mae</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Reston, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, RDS, Scala, ETL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d7c7e630377051dd</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Full Stack Engineer 4</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Capital One</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3c0579d402aad195</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Full-stack Engineer 4, Cyber Identity Security</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Capital One</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>McLean, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5c73541ffb28ff13</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Full-stack Engineer 4 (Java, Spring Boot, Python, CI/CD)</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Capital One</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>McLean, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cd55268246c76b99</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Full Stack Engineer 4</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Capital One</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5a68879b2db22f8d</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Senior Associate – Palantir Forward Deployed Engineer</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Fannie Mae</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Reston, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f170b110a592bbc2</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Site Reliability Engineer (IT Infrastructure Engineer 2) - Provisional</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>City University of New York</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, Oracle, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c2241815f02a7263</t>
+          <t>https://www.indeed.com/viewjob?jk=7fbd614b760e4ec5</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-10-04.xlsx
+++ b/results/job_matches_2026-10-04.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -590,41 +590,6 @@
       <c r="G5" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=4f386708dcb9013c</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Senior Cloud Engineer</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Slalom Consulting</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>AWS, S3, API Gateway, IAM, RDS, Azure, GCP, Scala, Snowflake, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7fbd614b760e4ec5</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-10-04.xlsx
+++ b/results/job_matches_2026-10-04.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -520,76 +520,6 @@
       <c r="G3" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=e7d5eebfd52c3041</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Government and Infrastructure - Cybersecurity - DevSecOps Senior Engineer</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>EY</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>McLean, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>RDS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Jenkins</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8204bb14afee5287</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Government and Infrastructure - Cybersecurity - DevSecOps Engineer</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>EY</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>McLean, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>RDS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Jenkins</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4f386708dcb9013c</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-10-04.xlsx
+++ b/results/job_matches_2026-10-04.xlsx
@@ -456,35 +456,35 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>API &amp; Data Engineer II</t>
+          <t>VMware VCF Administrator</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>First Advantage</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Tignall, GA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>15.3</v>
+        <v>12.5</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Spark, PySpark, Scala, Kafka</t>
+          <t>Azure, Scala, Oracle, PostgreSQL, MySQL, Cassandra, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3babb1e30d3465d</t>
+          <t>https://www.indeed.com/viewjob?jk=8730f563dbd095d7</t>
         </is>
       </c>
     </row>
